--- a/NoobToRoot.xlsx
+++ b/NoobToRoot.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OldToRoot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="DonnéesExternes_1" localSheetId="0" hidden="1">questions!$A$1:$N$64</definedName>
@@ -9534,4 +9535,9660 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N201"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5.7265625" customWidth="1" min="1" max="1"/>
+    <col width="9.54296875" customWidth="1" min="2" max="2"/>
+    <col width="10.81640625" customWidth="1" min="3" max="3"/>
+    <col width="59.453125" customWidth="1" min="4" max="4"/>
+    <col width="36.26953125" customWidth="1" min="5" max="5"/>
+    <col width="34.26953125" customWidth="1" min="7" max="7"/>
+    <col width="25.36328125" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="25.90625" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="49.1796875" customWidth="1" min="13" max="13"/>
+    <col width="80.54296875" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>langage</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>difficulte</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>reponse1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>reponse2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>reponse3</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>reponse4</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reponse5</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reponse6</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>leurre1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>leurre2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>indice</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>explication</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BA-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Afficher le texte BONJOUR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PRINT "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>? "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ECHO "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>WRITE "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Imprimer, en anglais</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>`PRINT` affiche à l'écran. Sur beaucoup de BASIC, `?` est un raccourci de PRINT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BA-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Écrire la ligne 10 du programme, qui affiche BONJOUR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10 PRINT "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10 ? "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PRINT 10 "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>LINE 10 PRINT "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Le numéro de ligne vient en premier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>En BASIC, chaque ligne commence par un numéro. On numérote de 10 en 10 pour pouvoir insérer des lignes plus tard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BA-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lancer le programme en mémoire</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RUN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>EXEC</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Courir, en anglais</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>`RUN` exécute le programme à partir de la plus petite ligne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BA-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Afficher le listing du programme</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SHOW</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Une liste</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>`LIST` affiche toutes les lignes. `LIST 10-50` n'en montre qu'une partie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BA-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Effacer entièrement le programme en mémoire</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>CLS</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ERASE</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Repartir à neuf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>`NEW` vide la mémoire du programme. `CLS` n'efface que l'écran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BA-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Effacer l'écran (GW-BASIC)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CLS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Clear screen, en trois lettres</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>`CLS` vide l'écran. `CLEAR` remet les variables à zéro, rien à voir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BA-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Écrire la ligne 20, qui renvoie à la ligne 10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20 GOTO 10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20 GO TO 10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>20 GOBACK 10</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>20 JUMP 10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Aller à, en anglais, collé</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>`GOTO` saute à une ligne. Avec la ligne 10 qui affiche un texte, on obtient la célèbre boucle infinie des magasins d'informatique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BA-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mettre la valeur 5 dans la variable A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A = 5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LET A = 5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>A := 5</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SET A = 5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Un simple signe égal</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>`LET` est facultatif sur la plupart des BASIC : `A = 5` suffit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BA-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Demander un nombre au clavier et le ranger dans N</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INPUT N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>READ N</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ASK N</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Entrée, en anglais</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>`INPUT` affiche un ? et attend la saisie. `READ` lit les valeurs des lignes DATA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BA-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Écrire un commentaire contenant SALUT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>REM SALUT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>' SALUT</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t># SALUT</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>// SALUT</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Abréviation de remark</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>`REM` (remarque) est ignoré à l'exécution. Plusieurs BASIC acceptent aussi l'apostrophe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BA-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Terminer le programme</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>QUIT</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>La fin, en anglais</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>`END` arrête le programme et rend la main avec READY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BA-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mettre le texte ADA dans la variable chaîne N$</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N$ = "ADA"</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LET N$ = "ADA"</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>N = "ADA"</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>$N = "ADA"</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Le dollar va à la fin du nom</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Le `$` final indique une variable texte. Sans lui, la variable ne peut contenir qu'un nombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BA-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Afficher le résultat de 3 + 4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PRINT 3 + 4</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>? 3 + 4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PRINT "3 + 4"</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>SUM 3 + 4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PRINT, et un calcul sans guillemets</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Sans guillemets, BASIC calcule et affiche 7. Entre guillemets, il afficherait le texte tel quel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BA-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sauvegarder le programme sous le nom JEU</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SAVE "JEU"</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>STORE "JEU"</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>WRITE "JEU"</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Sauver, en anglais</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>`SAVE` enregistre sur disquette ou cassette. Sur Commodore 64, on ajoutait `,8` pour viser le lecteur de disquette.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BA-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Charger le programme JEU</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LOAD "JEU"</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>OPEN "JEU"</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>GET "JEU"</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Charger, en anglais</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>`LOAD` ramène le programme en mémoire. Il faut ensuite taper RUN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BA-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Calculer la racine carrée de 16</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SQR(16)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PRINT SQR(16)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SQRT(16)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ROOT(16)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Trois lettres, sans T</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>En BASIC, la racine s'écrit `SQR`, alors que la plupart des langages modernes écrivent sqrt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BA-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Écrire la ligne 30, qui affiche la valeur de la variable A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>30 PRINT A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>30 ? A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>30 PRINT "A"</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>30 ECHO A</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Pas de guillemets autour du nom</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>`PRINT A` affiche la valeur. `PRINT "A"` afficherait juste la lettre A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BA-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Calculer la valeur absolue de -7</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ABS(-7)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PRINT ABS(-7)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ABSOLUTE(-7)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>VAL(-7)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Trois lettres</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>`ABS` renvoie 7. `VAL` sert à transformer un texte en nombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BA-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tirer un nombre au hasard entre 0 et 1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RND(1)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PRINT RND(1)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>RAND(1)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>RANDOM(1)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Random, en trois lettres</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>`RND(1)` donne un nombre décimal entre 0 et 1. On le multiplie pour obtenir d'autres plages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BA-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Obtenir la longueur de la chaîne N$</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LEN(N$)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PRINT LEN(N$)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>LENGTH(N$)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>SIZE(N$)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Abréviation de length</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>`LEN` compte les caractères, espaces compris.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BA-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Écrire la ligne 10, qui démarre une boucle I de 1 à 10</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10 FOR I = 1 TO 10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>10 FOR I = 1 TO 10 DO</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>10 LOOP I = 1 TO 10</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FOR… TO…</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>La boucle `FOR` se referme plus loin avec `NEXT I`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BA-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fermer la boucle FOR sur la variable I</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NEXT I</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>END FOR</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>LOOP I</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Au suivant !</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>`NEXT I` passe à la valeur suivante et remonte au FOR tant que la fin n'est pas atteinte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BA-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Si A est plus grand que 10, aller à la ligne 100</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IF A &gt; 10 THEN 100</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>IF A &gt; 10 THEN GOTO 100</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>IF A &gt; 10 GOTO 100</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>IF A &gt; 10 DO 100</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>IF (A &gt; 10) { GOTO 100 }</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>IF… THEN…</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Dans les vieux BASIC, `THEN` suivi d'un numéro de ligne vaut un GOTO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BA-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Appeler le sous-programme qui commence à la ligne 500</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GOSUB 500</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>CALL 500</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>GOTO SUB 500</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>GO + SUBroutine</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>`GOSUB` saute à la ligne 500 et retient d'où il vient, pour y revenir avec RETURN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BA-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Revenir d'un sous-programme</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RETURN</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>BACK</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ENDSUB</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Retour, en anglais</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>`RETURN` reprend juste après le GOSUB qui a appelé le sous-programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BA-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Stocker les valeurs 1, 2 et 3 dans le programme</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DATA 1, 2, 3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>VALUES 1, 2, 3</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ARRAY 1, 2, 3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Des données, en anglais</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Les lignes `DATA` contiennent des valeurs que `READ` lira une par une.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BA-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lire la prochaine valeur des lignes DATA dans X</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>READ X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>INPUT X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>LOAD X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Lire, en anglais</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>`READ` prend la valeur suivante dans les DATA. `RESTORE` revient à la première.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BA-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Réserver un tableau T de 10 éléments</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DIM T(10)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ARRAY T(10)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DIM T[10]</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Abréviation de dimension</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>`DIM` crée le tableau. Les éléments se lisent ensuite avec des parenthèses : `T(1)`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BA-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Prendre les 3 premiers caractères de N$</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LEFT$(N$, 3)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PRINT LEFT$(N$, 3)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>LEFT(N$, 3)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>FIRST$(N$, 3)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Gauche, avec un dollar</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Les fonctions qui renvoient du texte finissent par `$` : LEFT$, RIGHT$, MID$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BA-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Garder la partie entière de 3.7</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>INT(3.7)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PRINT INT(3.7)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ROUND(3.7)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>INTEGER(3.7)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Abréviation d'integer</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>`INT` arrondit vers le bas : `INT(3.7)` donne 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BA-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Afficher A puis B avec deux instructions sur la même ligne de programme</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PRINT "A" : PRINT "B"</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>? "A" : ? "B"</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>PRINT "A" &amp; PRINT "B"</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PRINT "A" / PRINT "B"</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Le deux-points sépare les instructions</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Le `:` permet d'enchaîner plusieurs instructions sur une ligne. Indispensable quand la mémoire se comptait en kilo-octets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BA-32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Écrire une boucle I de 10 à 0, de 2 en 2 vers le bas</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>FOR I = 10 TO 0 STEP -2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>FOR I = 10 TO 0 BY -2</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>FOR I = 10 DOWNTO 0 STEP 2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>STEP, avec un pas négatif</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>`STEP` règle le pas. Sans lui, la boucle avance de 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BA-33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Extraire 2 caractères de N$ à partir du 3e</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MID$(N$, 3, 2)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PRINT MID$(N$, 3, 2)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>MID$(N$, 2, 3)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SUBSTR$(N$, 3, 2)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Le milieu : position, puis longueur</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>`MID$(chaîne, début, longueur)`. Les positions commencent à 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BA-34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Obtenir le caractère dont le code ASCII est 65</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CHR$(65)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PRINT CHR$(65)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ASC(65)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CHAR(65)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Character, avec un dollar</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>`CHR$(65)` donne A. La fonction inverse, `ASC`, donne le code d'un caractère.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BA-35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Convertir le nombre 42 en chaîne</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>STR$(42)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PRINT STR$(42)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>STRING(42)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>TEXT$(42)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>String, en trois lettres et un dollar</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>`STR$` transforme un nombre en texte. Attention, il ajoute souvent un espace devant pour le signe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BA-36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Convertir la chaîne "42" en nombre</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>VAL("42")</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PRINT VAL("42")</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>INT("42")</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NUM("42")</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Valeur, en trois lettres</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>`VAL` lit un nombre dans un texte. `INT` attend déjà un nombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BA-37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tirer un nombre entier au hasard de 1 à 6, comme un dé</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>INT(RND(1) * 6) + 1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1 + INT(RND(1) * 6)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>INT(6 * RND(1)) + 1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1 + INT(6 * RND(1))</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>INT(RND(1) * 6)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>RND(1) * 6 + 1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>RND, multiplié, INT, puis +1</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>`RND(1) * 6` donne de 0 à 5.99. `INT` garde 0 à 5, et `+ 1` décale de 1 à 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BA-38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Commodore 64 : écrire la valeur 0 à l'adresse 53280 (bordure noire)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>POKE 53280, 0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PEEK 53280, 0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>SET 53280, 0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Pousser une valeur dans la mémoire</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>`POKE adresse, valeur` écrit directement dans la mémoire. Sur C64, 53280 est la couleur de la bordure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BA-39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lire la valeur stockée à l'adresse mémoire 53280</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEEK(53280)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PRINT PEEK(53280)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>POKE(53280)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>READ(53280)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Jeter un œil, en anglais</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>`PEEK` lit la mémoire, `POKE` l'écrit. Le duo des bidouilleurs des années 80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BA-40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Aller à la ligne 100, 200 ou 300 selon que X vaut 1, 2 ou 3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ON X GOTO 100, 200, 300</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>SWITCH X GOTO 100, 200, 300</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>GOTO X OF 100, 200, 300</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>ON… GOTO…</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>`ON X GOTO` choisit la destination selon la valeur de X : l'ancêtre du switch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DO-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lister les fichiers du dossier courant</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Abréviation de directory</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>`DIR` liste les fichiers avec leur taille et leur date. L'équivalent Linux est ls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DO-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Entrer dans le dossier JEUX</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CD JEUX</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CHDIR JEUX</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>GO JEUX</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>OPEN JEUX</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Change directory</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>`CD` change de dossier, exactement comme sous Linux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DO-03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Remonter au dossier parent</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CD ..</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CD..</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>CD /</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>BACK</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Deux points</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>`..` désigne le dossier parent. DOS accepte même `CD..` sans espace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DO-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Revenir à la racine du disque</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CD \</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CD\</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>CD ~</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CD /</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>La barre oblique inverse</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Sous DOS, les dossiers sont séparés par `\`, et non par `/` comme sous Linux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DO-05</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Effacer l'écran</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CLS</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>ERASE</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Clear screen</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>`CLS` vide l'écran. C'est aussi la commande BASIC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DO-06</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Créer le dossier JEUX</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MD JEUX</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MKDIR JEUX</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NEWDIR JEUX</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CD JEUX</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Make directory</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>`MD` ou `MKDIR` créent un dossier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DO-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Supprimer le fichier NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DEL NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ERASE NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>RM NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>REMOVE NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Abréviation de delete</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>`DEL` supprime un fichier. Pas de corbeille sous DOS !</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DO-08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Afficher le contenu du fichier NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>TYPE NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>CAT NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>SHOW NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Taper, comme une machine à écrire</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>`TYPE` affiche un fichier texte. L'équivalent Linux est cat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DO-09</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Copier NOTES.TXT vers COPIE.TXT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>COPY NOTES.TXT COPIE.TXT</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>CP NOTES.TXT COPIE.TXT</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>DUP NOTES.TXT COPIE.TXT</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Copier, en anglais</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>`COPY source destination`. L'original reste en place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DO-10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Renommer VIEUX.TXT en NEUF.TXT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>REN VIEUX.TXT NEUF.TXT</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>RENAME VIEUX.TXT NEUF.TXT</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>MV VIEUX.TXT NEUF.TXT</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NAME VIEUX.TXT NEUF.TXT</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Abréviation de rename</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>`REN` renomme sans déplacer. Les noms DOS faisaient au plus 8 caractères, plus 3 pour l'extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DO-11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Passer sur le lecteur de disquette A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>A:</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>CD A:</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>GO A</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>La lettre du lecteur et deux-points</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Taper simplement `A:` change de lecteur. `C:` ramène au disque dur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DO-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Afficher la version de MS-DOS</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>VER</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>VERSION</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>DOSVER</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Trois lettres</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>`VER` affiche par exemple « MS-DOS Version 6.22 ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DO-13</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Afficher ou modifier la date du système</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>TODAY</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Le mot anglais, tout simplement</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>`DATE` affiche la date et propose d'en saisir une nouvelle. Entrée garde la date actuelle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DO-14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Afficher ou modifier l'heure du système</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>CLOCK</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>HOUR</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Temps, en anglais</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>`TIME` fonctionne comme DATE : affichage, puis saisie facultative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DO-15</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Supprimer le dossier vide JEUX</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RD JEUX</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>RMDIR JEUX</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>DEL JEUX</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>DELDIR JEUX</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Remove directory</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>`RD` ne supprime qu'un dossier vide. `DEL JEUX` effacerait les fichiers qu'il contient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DO-16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Afficher l'aide de la commande DIR</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DIR /?</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>HELP DIR</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>MAN DIR</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DIR --HELP</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Un point d'interrogation après une barre</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Sous DOS, les options commencent par `/`. `/?` affiche l'aide de presque toutes les commandes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DO-17</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lister les fichiers en format large, sur plusieurs colonnes</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DIR /W</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>DIR -W</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DIR /LARGE</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>W pour wide</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>`/W` affiche les noms en colonnes, sans taille ni date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DO-18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lister les fichiers page par page</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DIR /P</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>DIR /PAGE</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DIR -P</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>P pour pause</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>`/P` s'arrête à chaque écran plein et attend une touche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DO-19</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Afficher le message BONJOUR</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ECHO BONJOUR</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>PRINT BONJOUR</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>SAY BONJOUR</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Le terminal renvoie l'écho</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>`ECHO` affiche du texte. Très utilisé dans les fichiers .BAT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DO-20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Formater la disquette du lecteur A</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FORMAT A:</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ERASE A:</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>CLEAN A:</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Le mot est le même en français</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>`FORMAT` efface et prépare un disque. Attention : `FORMAT C:` effaçait le disque dur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DO-21</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lister uniquement les fichiers .TXT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DIR *.TXT</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>DIR TXT</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DIR %.TXT</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Une étoile comme joker</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>`*` remplace n'importe quel nom. `?` remplace un seul caractère.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DO-22</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Copier tous les fichiers .TXT vers la disquette A</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>COPY *.TXT A:</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>COPY *.TXT A:\</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>COPY A: *.TXT</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>MOVE ALL .TXT A:</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>COPY, le joker, puis la destination</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>La source vient toujours en premier, la destination en second.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DO-23</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lister les fichiers en incluant tous les sous-dossiers</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DIR /S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>DIR /R</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>DIR /ALL</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>S pour subdirectories</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>`DIR /S` parcourt toute l'arborescence. Pratique pour retrouver un fichier perdu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DO-24</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Afficher l'arborescence des dossiers</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>TREE</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>DIR /T</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Un arbre, en anglais</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>`TREE` dessine les dossiers avec des traits. `TREE /F` ajoute les fichiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DO-25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ouvrir le fichier CONFIG.SYS dans l'éditeur de texte</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>EDIT CONFIG.SYS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>OPEN CONFIG.SYS</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>VI CONFIG.SYS</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Éditer, en anglais</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>`EDIT` ouvre l'éditeur plein écran bleu de MS-DOS 5 et 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DO-26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Afficher NOTES.TXT page par page en passant par MORE</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TYPE NOTES.TXT | MORE</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MORE &lt; NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>TYPE NOTES.TXT &gt; MORE</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>TYPE NOTES.TXT /P</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Un tube, comme sous Linux</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Le `|` envoie la sortie de TYPE à MORE, qui s'arrête à chaque page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DO-27</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Écrire la liste des fichiers dans LISTE.TXT, en écrasant son contenu</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DIR &gt; LISTE.TXT</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>DIR &gt;&gt; LISTE.TXT</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>DIR | LISTE.TXT</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Un seul chevron</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>`&gt;` écrase le fichier, `&gt;&gt;` ajoute à la fin. Même logique que sous Linux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DO-28</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Afficher la mémoire disponible</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Abréviation de memory</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>`MEM` montre la mémoire conventionnelle, les fameux 640 Ko, et la mémoire étendue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DO-29</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Vérifier le disque C avec l'utilitaire historique de vérification</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>CHKDSK C:</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CHKDSK</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>CHECK C:</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>FSCK C:</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Check disk, sans voyelles</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>`CHKDSK` vérifie le disque. ScanDisk l'a remplacé à partir de MS-DOS 6.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DO-30</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Afficher les dossiers où DOS cherche les programmes</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ECHO PATH</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>SHOW PATH</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Le chemin, en anglais</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>`PATH` seul affiche la liste. On la définit en général dans AUTOEXEC.BAT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DO-31</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Changer l'invite pour afficher le chemin suivi de &gt;</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PROMPT $P$G</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>PROMPT %P%G</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>PROMPT P&gt;</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Des dollars : P pour path, G pour greater than</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>`$P` affiche le chemin, `$G` le signe &gt;. D'où le célèbre `C:\&gt;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DO-32</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Créer la variable d'environnement NOM, qui vaut ADA</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SET NOM=ADA</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>NOM=ADA</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>LET NOM=ADA</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>SET, le nom, égal, la valeur</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>`SET` crée la variable. Attention : sous DOS, un espace avant le `=` fait partie du nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DO-33</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Afficher la valeur de la variable NOM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ECHO %NOM%</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ECHO $NOM</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>ECHO NOM</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Encadrée par des pourcentages</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Sous DOS, une variable se lit entre deux `%`. Sous Linux, on écrirait `$NOM`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DO-34</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Copier le dossier JEUX et ses sous-dossiers vers la disquette A</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>XCOPY JEUX A:\ /S</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>XCOPY JEUX A: /S</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>XCOPY JEUX A:\ /S /E</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>XCOPY JEUX A: /S /E</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>COPY JEUX A: /S</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>COPY -R JEUX A:</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Une copie étendue, avec l'option des sous-dossiers</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>`XCOPY /S` copie l'arborescence. `/E` copie aussi les dossiers vides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DO-35</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mettre le fichier NOTES.TXT en lecture seule</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ATTRIB +R NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ATTRIB -R NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>CHMOD +R NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Attribut, plus R pour read-only</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>`+` ajoute un attribut, `-` le retire. H masque le fichier, S en fait un fichier système.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DO-36</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Dans un fichier .BAT, ne plus afficher les commandes exécutées</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>@ECHO OFF</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ECHO OFF</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ECHO NONE</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>SILENT ON</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>ECHO, éteint</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>`@ECHO OFF` en première ligne : le `@` cache même cette commande-là.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DO-37</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Dans un fichier .BAT, attendre que l'utilisateur appuie sur une touche</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PAUSE</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>GETKEY</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Une pause</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>`PAUSE` affiche « Appuyez sur une touche pour continuer… ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DO-38</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Dans un fichier .BAT, sauter à l'étiquette :FIN</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>GOTO FIN</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>JUMP FIN</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>GOSUB FIN</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Comme en BASIC</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>L'étiquette s'écrit `:FIN` sur sa propre ligne, et `GOTO FIN` y saute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DO-39</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Afficher NOTES.TXT seulement si ce fichier existe</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>IF EXIST NOTES.TXT TYPE NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>IF NOTES.TXT EXISTS TYPE NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>IF FOUND NOTES.TXT TYPE NOTES.TXT</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>IF, puis un mot qui signifie exister</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>`IF EXIST fichier commande` : le test le plus courant des scripts DOS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DO-40</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>msdos</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Quel fichier .BAT MS-DOS exécute-t-il automatiquement au démarrage ?</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AUTOEXEC.BAT</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>STARTUP.BAT</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>BOOT.BAT</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Exécution automatique</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>`AUTOEXEC.BAT` définissait le PATH, le clavier français et lançait les pilotes. `CONFIG.SYS` était lu juste avant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CO-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Afficher le texte BONJOUR</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DISPLAY "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>PRINT "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>WRITE "BONJOUR"</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Afficher, en anglais</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>`DISPLAY` affiche à l'écran. `WRITE` sert à écrire dans un fichier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CO-02</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Arrêter le programme</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>STOP RUN</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>END RUN</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>STOP PROGRAM</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Arrête la course</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>`STOP RUN` termine l'exécution et rend la main au système.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CO-03</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Mettre la valeur 5 dans la variable A</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>MOVE 5 TO A</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>A = 5</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>PUT 5 IN A</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Déplacer… vers…</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>En COBOL, on ne note pas `A = 5` : on « déplace » la valeur vers la variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CO-04</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Recopier la valeur de A dans B</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>MOVE A TO B</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>MOVE B TO A</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>B = A</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>La source d'abord, la destination ensuite</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>`MOVE A TO B` : A reste inchangé, B reçoit sa valeur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CO-05</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Ajouter 1 à la variable COMPTEUR</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ADD 1 TO COMPTEUR</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>COMPTEUR += 1</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>PLUS 1 TO COMPTEUR</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Ajouter, en anglais</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Les opérations s'écrivent comme des phrases : ADD, SUBTRACT, MULTIPLY, DIVIDE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CO-06</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Retirer 2 de la variable TOTAL</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>SUBTRACT 2 FROM TOTAL</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>MINUS 2 FROM TOTAL</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>SUBTRACT TOTAL FROM 2</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Soustraire… de…</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>`SUBTRACT 2 FROM TOTAL` range le résultat dans TOTAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CO-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lire une saisie au clavier dans la variable NOM</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ACCEPT NOM</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>INPUT NOM</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>READ NOM</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Accepter, en anglais</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>`ACCEPT` attend la saisie. `READ` lit un enregistrement dans un fichier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CO-08</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Écrire l'en-tête de la première division d'un programme</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>IDENTIFICATION DIVISION</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>HEADER DIVISION</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>PROGRAM DIVISION</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>La division qui identifie le programme</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Un programme COBOL compte quatre divisions : IDENTIFICATION, ENVIRONMENT, DATA et PROCEDURE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CO-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Donner le nom BONJOUR au programme</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PROGRAM-ID. BONJOUR</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>PROGRAM BONJOUR</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NAME-ID. BONJOUR</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>PROGRAM, un tiret, ID, un point</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>`PROGRAM-ID.` est la seule ligne obligatoire de l'IDENTIFICATION DIVISION.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CO-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Écrire l'en-tête de la division qui décrit l'environnement</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT DIVISION</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>SYSTEM DIVISION</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>CONFIG DIVISION</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Environnement, en anglais</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>L'ENVIRONMENT DIVISION décrit la machine et les fichiers utilisés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CO-11</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Écrire l'en-tête de la division des données</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DATA DIVISION</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>VARIABLE DIVISION</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>MEMORY DIVISION</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Données, en anglais</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Toutes les variables sont déclarées dans la DATA DIVISION, avant le code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CO-12</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Écrire l'en-tête de la section des variables de travail</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>WORKING-STORAGE SECTION</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>VARIABLE SECTION</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>WORK SECTION</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Le stockage de travail, avec un tiret</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>La WORKING-STORAGE SECTION contient les variables du programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CO-13</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Écrire l'en-tête de la division qui contient les instructions</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PROCEDURE DIVISION</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>CODE DIVISION</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>MAIN DIVISION</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Procédure, en anglais</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Le code exécutable commence après `PROCEDURE DIVISION.`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CO-14</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Afficher la valeur de la variable NOM</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>DISPLAY NOM</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>DISPLAY "NOM"</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>PRINT NOM</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Pas de guillemets autour du nom</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Entre guillemets, COBOL afficherait le mot NOM et non son contenu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CO-15</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Afficher BONJOUR suivi du contenu de la variable NOM</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>DISPLAY "BONJOUR " NOM</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DISPLAY "BONJOUR" NOM</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>DISPLAY "BONJOUR" + NOM</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>DISPLAY "BONJOUR" &amp; NOM</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Il suffit de les mettre côte à côte</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>`DISPLAY` affiche à la suite tout ce qu'on lui donne, séparé par des espaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CO-16</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Afficher les variables NOM et PRENOM à la suite</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>DISPLAY NOM PRENOM</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>DISPLAY NOM + PRENOM</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>DISPLAY NOM &amp; PRENOM</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Côte à côte, sans opérateur</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Aucun opérateur de concaténation n'est nécessaire pour afficher plusieurs éléments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CO-17</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Avec quels symboles commence un commentaire en COBOL moderne (format libre) ?</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>*&gt;</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>re:^\*&gt;.*</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Une étoile et un chevron</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>`*&gt;` commente la fin de ligne. En format fixe, on mettait une étoile en colonne 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CO-18</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Remplir la variable NOM d'espaces pour la vider</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>MOVE SPACES TO NOM</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>MOVE SPACE TO NOM</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>MOVE "" TO NOM</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>CLEAR NOM</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Des espaces, en anglais</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>`SPACES` est une constante figurative. Il existe aussi `ZERO` et `HIGH-VALUES`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CO-19</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Mettre zéro dans la variable TOTAL</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>MOVE ZERO TO TOTAL</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>MOVE ZEROS TO TOTAL</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>MOVE ZEROES TO TOTAL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>MOVE 0 TO TOTAL</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>TOTAL = 0</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>RESET TOTAL</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>MOVE, la constante zéro, TO</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>`ZERO`, `ZEROS` et `ZEROES` sont synonymes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CO-20</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Fermer un bloc IF</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>END-IF</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ENDIF</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>END IF</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>END, un tiret, IF</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Les terminateurs explicites (END-IF, END-PERFORM…) sont arrivés avec COBOL 85.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CO-21</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Multiplier la variable PRIX par 2, résultat dans PRIX</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>MULTIPLY 2 BY PRIX</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>MULTIPLY PRIX BY 2</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>PRIX = PRIX * 2</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Le résultat va dans ce qui suit BY</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>`MULTIPLY 2 BY PRIX` range le résultat dans PRIX. Le nombre 2 ne peut pas recevoir de valeur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>CO-22</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Diviser la variable TOTAL par 2, résultat dans TOTAL</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>DIVIDE 2 INTO TOTAL</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>DIVIDE 2 FROM TOTAL</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>TOTAL = TOTAL / 2</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Diviser… dans…</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>`DIVIDE 2 INTO TOTAL` range le résultat dans TOTAL. Avec BY, il faut ajouter GIVING.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CO-23</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Déclarer au niveau 01 la variable AGE, un nombre de 2 chiffres</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>01 AGE PIC 99</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>01 AGE PIC 9(2)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>01 AGE PIC IS 99</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>01 AGE PICTURE 99</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>01 AGE INT 2</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>01 AGE PIC X(2)</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>PIC, et un 9 par chiffre</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>`PIC` (picture) décrit le format : `9` pour un chiffre, `X` pour un caractère.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CO-24</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Déclarer au niveau 01 la variable NOM, un texte de 20 caractères</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>01 NOM PIC X(20)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>01 NOM PICTURE X(20)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>01 NOM PIC 9(20)</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>01 NOM STRING(20)</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>PIC, et X pour un caractère</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>`X(20)` signifie 20 caractères quelconques. La taille est fixe, pas de chaîne extensible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CO-25</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Calculer TOTAL = PRIX × QTE</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>COMPUTE TOTAL = PRIX * QTE</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>COMPUTE TOTAL = QTE * PRIX</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>TOTAL = PRIX * QTE</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>CALCULATE TOTAL = PRIX * QTE</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Calculer, en anglais</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>`COMPUTE` est la seule instruction qui accepte des formules mathématiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CO-26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Additionner A et B, résultat dans C</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ADD A TO B GIVING C</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ADD A B GIVING C</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>ADD A TO B INTO C</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>C = A + B</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Le résultat est donné avec un mot-clé</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>`GIVING` range le résultat ailleurs, sans modifier A ni B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CO-27</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Exécuter le paragraphe CALCUL</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PERFORM CALCUL</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>CALL CALCUL</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>GOSUB CALCUL</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Exécuter, en anglais</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>`PERFORM` exécute un paragraphe puis revient. `CALL` appelle un autre programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CO-28</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Exécuter 3 fois le paragraphe AFFICHE</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PERFORM AFFICHE 3 TIMES</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>PERFORM AFFICHE * 3</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>REPEAT AFFICHE 3</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>PERFORM… TIMES</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>`PERFORM paragraphe n TIMES` : la boucle la plus simple de COBOL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CO-29</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Écrire le début d'un test : si AGE est plus grand que 17</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>IF AGE &gt; 17</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>IF AGE &gt; 17 THEN</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>IF AGE GREATER THAN 17</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>IF AGE IS GREATER THAN 17</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>IF AGE GREATER 17</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>IF (AGE &gt; 17) {</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>IF AGE &gt; 17 DO</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>IF, puis la condition, en symbole ou en anglais</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>COBOL accepte `&gt;` ou `GREATER THAN`. Le bloc se ferme par END-IF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CO-30</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Déclarer TOTAL, un nombre de 3 chiffres, initialisé à 0</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>01 TOTAL PIC 9(3) VALUE 0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>01 TOTAL PIC 9(3) VALUE ZERO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>01 TOTAL PIC 999 VALUE 0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>01 TOTAL PIC 999 VALUE ZERO</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>01 TOTAL PIC 9(3) VALUE ZEROS</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>01 TOTAL PIC 9(3) VALUE IS 0</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>01 TOTAL PIC 9(3) = 0</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>01 TOTAL PIC 9(3) INIT 0</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>VALUE, après le PIC</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>`VALUE` donne la valeur de départ au lancement du programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CO-31</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Exécuter le paragraphe CALCUL jusqu'à ce que I dépasse 10</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PERFORM CALCUL UNTIL I &gt; 10</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>PERFORM CALCUL UNTIL I GREATER THAN 10</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>PERFORM CALCUL WHILE I &gt; 10</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>LOOP CALCUL UNTIL I &gt; 10</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>PERFORM… UNTIL…</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>La condition est testée avant chaque passage : si elle est vraie dès le départ, rien n'est exécuté.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CO-32</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Exécuter AFFICHE pour I allant de 1 à 10, de 1 en 1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PERFORM AFFICHE VARYING I FROM 1 BY 1 UNTIL I &gt; 10</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>PERFORM AFFICHE FOR I = 1 TO 10</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>PERFORM AFFICHE VARYING I 1 TO 10</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>VARYING… FROM… BY… UNTIL…</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>C'est la boucle FOR de COBOL. Elle s'arrête quand la condition UNTIL devient vraie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CO-33</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Déclarer PRIX : 4 chiffres avant la virgule et 2 après</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>01 PRIX PIC 9(4)V99</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>01 PRIX PIC 9(4)V9(2)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>01 PRIX PIC 9999V99</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>01 PRIX PIC 9(4)D99</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>01 PRIX PIC DECIMAL(4,2)</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Un V marque la virgule</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Le `V` est une virgule virtuelle : elle compte dans les calculs mais n'occupe pas de place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CO-34</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>3</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Déclarer SOLDE, un nombre signé de 5 chiffres</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>01 SOLDE PIC S9(5)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>01 SOLDE PIC S99999</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>01 SOLDE PIC 9(5)S</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>01 SOLDE SIGNED PIC 9(5)</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Une lettre devant les 9</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Le `S` en tête permet de stocker des valeurs négatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CO-35</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Déclarer la condition MAJEUR, vraie quand la variable vaut de 18 à 99</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>88 MAJEUR VALUE 18 THRU 99</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>88 MAJEUR VALUE 18 THROUGH 99</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>88 MAJEUR VALUES 18 THRU 99</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>88 MAJEUR VALUES ARE 18 THRU 99</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>77 MAJEUR VALUE 18 THRU 99</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>88 MAJEUR = 18 TO 99</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Le niveau 88, et THRU</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Un niveau 88 nomme une condition. On écrit ensuite simplement `IF MAJEUR`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CO-36</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Commencer un choix multiple sur la variable CHOIX</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>EVALUATE CHOIX</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>SWITCH CHOIX</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>CASE CHOIX</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Évaluer, en anglais</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>`EVALUATE` est le switch de COBOL. Il se termine par END-EVALUATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CO-37</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Dans un EVALUATE, écrire le cas où la valeur vaut 1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>WHEN 1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>CASE 1</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>IF 1</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Quand, en anglais</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Chaque cas commence par `WHEN`. `WHEN OTHER` traite tous les autres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CO-38</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Ouvrir le fichier CLIENTS en lecture</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>OPEN INPUT CLIENTS</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>OPEN READ CLIENTS</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>OPEN CLIENTS FOR INPUT</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>OPEN, puis le mode</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Les modes sont INPUT (lecture), OUTPUT (écriture), I-O et EXTEND (ajout).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CO-39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Lire l'enregistrement suivant du fichier CLIENTS</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>READ CLIENTS</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>READ CLIENTS NEXT</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>READ CLIENTS NEXT RECORD</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>ACCEPT CLIENTS</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>GET CLIENTS</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Lire, en anglais</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>`READ` lit un enregistrement. On ajoute souvent `AT END` pour détecter la fin du fichier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CO-40</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>cobol</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Fermer le fichier CLIENTS</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>CLOSE CLIENTS</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>END CLIENTS</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>STOP CLIENTS</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Fermer, en anglais</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Tout fichier ouvert par OPEN doit être fermé par `CLOSE` avant STOP RUN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PA-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Afficher Bonjour, puis passer à la ligne</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>writeln('Bonjour');</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>print('Bonjour');</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>echo('Bonjour');</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Write line</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>`writeln` affiche puis passe à la ligne. Le texte va entre apostrophes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PA-02</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Afficher Bonjour sans passer à la ligne</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>write('Bonjour');</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>writeln('Bonjour');</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>put('Bonjour');</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Sans le ln</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>`write` reste sur la même ligne, `writeln` ajoute un retour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PA-03</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Mettre la valeur 5 dans la variable x</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>x := 5;</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>x = 5;</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>x == 5;</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Deux-points et égal</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>`:=` affecte une valeur. Le `=` seul sert à comparer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PA-04</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Ouvrir un bloc d'instructions</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>begin</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>{</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Commencer, en anglais</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>`begin` ouvre un bloc, `end` le ferme. En Pascal, les accolades servent aux commentaires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PA-05</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Écrire la toute dernière ligne d'un programme</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>end.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>end;</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>stop.</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>end, avec un point</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Le programme se termine par `end.` avec un point. Les autres blocs finissent par `end;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PA-06</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Donner le nom Jeu au programme</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>program Jeu;</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>programme Jeu;</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>name Jeu;</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Programme, en anglais</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>`program Jeu;` est la première ligne d'un programme Pascal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PA-07</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Écrire le mot-clé qui ouvre la section des variables</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>var</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>let</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Abréviation de variable</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Les variables sont toutes déclarées dans la section `var`, avant le begin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PA-08</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Déclarer la variable x comme un entier</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>x: integer;</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>var x: integer;</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>int x;</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>x: int;</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Nom, deux-points, type</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>En Pascal, le type vient après le nom : `x: integer`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PA-09</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Déclarer la variable prix comme un nombre décimal</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>prix: real;</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>var prix: real;</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>prix: float;</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>real prix;</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Réel, en anglais</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>`real` stocke les nombres à virgule. `float`, c'est en C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PA-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Déclarer la variable nom comme une chaîne de caractères</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>nom: string;</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>var nom: string;</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>nom: text;</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>string nom;</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Chaîne, en anglais</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Le type `string` est arrivé avec Turbo Pascal. `string[20]` limite la longueur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>PA-11</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Déclarer la variable ok comme un booléen</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ok: boolean;</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>var ok: boolean;</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>ok: bool;</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>ok: logical;</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Le nom complet, en hommage à Boole</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>`boolean` vaut `true` ou `false`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PA-12</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Lire une saisie au clavier dans la variable x</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>readln(x);</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>read(x);</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>input(x);</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>scanf(x);</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Read line</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>`readln` lit la saisie et attend la touche Entrée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PA-13</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Écrire un commentaire contenant note</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>{ note }</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>(* note *)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>re:^\{.*\}$</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>re:^\(\*.*\*\)$</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t># note</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>&lt;!-- note --&gt;</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Des accolades</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Pascal accepte `{ … }` et `(* … *)`. Les compilateurs récents acceptent aussi `//`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PA-14</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Quel opérateur signifie « différent de » ?</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>&lt;&gt;</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>!=</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>=/=</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Plus petit et plus grand à la fois</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>`&lt;&gt;` se lit « inférieur ou supérieur », donc différent. `!=` vient du C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>PA-15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Calculer la division entière de 7 par 2</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>7 div 2</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>7 / 2</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>7 // 2</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Un mot de trois lettres</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>`div` donne 3. `/` donne toujours un réel : 3.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PA-16</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Calculer le reste de la division de 7 par 2</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>7 mod 2</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>7 % 2</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>7 rem 2</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Abréviation de modulo</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>`mod` donne 1. Le `%` vient du C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PA-17</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Tester si x est égal à y</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>x = y</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>x == y</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>x := y</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Un seul signe égal</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>En Pascal, `=` compare et `:=` affecte : impossible de les confondre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>PA-18</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Écrire la valeur booléenne vrai</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Vrai, en anglais</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>`true` et `false` sont des mots-clés du type boolean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>PA-19</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Déclarer la constante PI qui vaut 3.14</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>const PI = 3.14;</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>const PI := 3.14;</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>PI = const 3.14;</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>const, puis un simple égal</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Les constantes utilisent `=` et non `:=`, car leur valeur est fixée à la compilation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>PA-20</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Afficher les variables x et y à la suite</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>writeln(x, y);</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>write(x, y);</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>writeln(x &amp; y);</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>writeln(x . y);</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Séparées par une virgule</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>`writeln` accepte plusieurs valeurs séparées par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>PA-21</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Écrire le début d'une boucle i de 1 à 10</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>for i := 1 to 10 do</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>for i = 1 to 10 do</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>for (i = 1; i &lt;= 10; i++)</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>for… := … to … do</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>La boucle répète l'instruction qui suit `do`, ou un bloc begin…end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PA-22</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Écrire le début d'une boucle i de 10 à 1, en descendant</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>for i := 10 downto 1 do</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>for i := 10 to 1 step -1 do</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>for i := 10 down to 1 do</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Vers le bas, en un seul mot</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>`downto` remplace `to` pour descendre. Pascal n'a pas de pas personnalisé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>PA-23</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Écrire le début d'un test : si x est plus grand que 10</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>if x &gt; 10 then</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>if (x &gt; 10) {</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>if x &gt; 10 do</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>if… then</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Pas besoin de parenthèses autour de la condition simple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>PA-24</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Écrire le début d'une boucle qui tourne tant que x est positif</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>while x &gt; 0 do</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>while x &gt; 0 then</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>while (x &gt; 0) {</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>while… do</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>`while` teste la condition avant chaque tour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PA-25</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Terminer une boucle repeat quand x vaut 0</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>until x = 0;</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>until x == 0;</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>while x &lt;&gt; 0;</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Jusqu'à, en anglais</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>`repeat … until` s'exécute au moins une fois : le test est à la fin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PA-26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Déclarer t, un tableau de 10 entiers numérotés de 1 à 10</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>t: array[1..10] of integer;</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>var t: array[1..10] of integer;</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>t: array[10] of integer;</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>t: integer[10];</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>array[début..fin] of type</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Pascal choisit les bornes : on peut écrire `array[0..9]` ou même `array['a'..'z']`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PA-27</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Obtenir la longueur de la chaîne nom</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>length(nom)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>len(nom)</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>nom.length</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Le mot anglais en entier</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>`length` renvoie le nombre de caractères.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>PA-28</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Ajouter 1 à la variable x</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>inc(x);</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>x := x + 1;</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>x++;</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>x =+ 1;</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Une procédure de trois lettres, ou l'affectation classique</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>`inc(x)` est plus rapide que `x := x + 1`. `dec(x)` fait l'inverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PA-29</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Calculer la racine carrée de 16</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>sqrt(16)</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>sqr(16)</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>root(16)</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Square root</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Attention : `sqrt` est la racine, `sqr` est le carré !</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PA-30</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Effacer l'écran (unité Crt de Turbo Pascal)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>clrscr;</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>cls;</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>clear;</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Clear screen, sans voyelles</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>`clrscr` vient de l'unité Crt, avec `gotoxy` et `textcolor`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PA-31</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>3</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Utiliser l'unité Crt</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>uses crt;</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>import crt;</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>include crt;</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Utiliser, en anglais</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>`uses` se place juste après la ligne program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PA-32</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>3</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne d'une procédure Saluer, sans paramètre</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>procedure Saluer;</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>function Saluer;</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>void Saluer;</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Une procédure ne renvoie rien</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Pascal sépare `procedure` (aucune valeur renvoyée) et `function` (une valeur renvoyée).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PA-33</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne de la fonction Carre, qui reçoit l'entier x et renvoie un entier</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>function Carre(x: integer): integer;</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>procedure Carre(x: integer): integer;</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>function Carre(x): integer;</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>function, paramètre typé, puis le type renvoyé</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Le type du résultat vient après les parenthèses. Dans le corps, on écrit `Carre := x * x;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PA-34</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>3</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne de la procédure Echange, qui modifie les entiers a et b</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>procedure Echange(var a, b: integer);</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>procedure Echange(ref a, b: integer);</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>procedure Echange(&amp;a, &amp;b: integer);</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Le même mot que pour déclarer les variables</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>`var` devant les paramètres passe les variables par référence : la procédure peut les modifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PA-35</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Commencer un choix multiple sur la variable choix</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>case choix of</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>switch choix of</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>case choix do</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>case… of</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Chaque cas s'écrit `1: instruction;`, et le bloc se ferme par `end;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PA-36</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>3</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Commencer la déclaration du type enregistrement Point</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>type Point = record</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Point = record</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>type Point = struct</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>type Point: record</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Un enregistrement, en anglais</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>`record` regroupe plusieurs champs, comme une struct en C. Le bloc se ferme par `end;`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>PA-37</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>3</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Déclarer p comme un pointeur vers un entier</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>p: ^integer;</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>var p: ^integer;</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>p: *integer;</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>p: &amp;integer;</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Un accent circonflexe</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>`^integer` est un pointeur. `p^` accède à la valeur pointée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PA-38</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>3</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Tester si le caractère c est une lettre minuscule</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>if c in ['a'..'z'] then</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>if c in ('a'..'z') then</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>if c between 'a' and 'z' then</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>in, et un ensemble entre crochets</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Les ensembles sont une spécialité de Pascal : `in` teste l'appartenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PA-39</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>3</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Associer la variable fichier f au fichier notes.txt</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>assign(f, 'notes.txt');</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>open(f, 'notes.txt');</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>fopen(f, 'notes.txt');</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Assigner, en anglais</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>En Turbo Pascal, `assign` lie la variable au nom du fichier, puis `reset` ou `rewrite` l'ouvre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PA-40</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>pascal</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>3</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Calculer le carré de 4</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>sqr(4)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>4 * 4</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>sqrt(4)</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>pow(4)</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Square, sans le t</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>`sqr(4)` donne 16. Ne pas confondre avec `sqrt`, la racine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>FO-01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Afficher le texte Bonjour</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>print *, 'Bonjour'</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>write(*,*) 'Bonjour'</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>print 'Bonjour'</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>echo 'Bonjour'</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>print, une étoile, une virgule</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>L'étoile signifie « format libre » : Fortran choisit seul la mise en forme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>FO-02</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Commencer le programme jeu</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>program jeu</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>begin jeu</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>programme jeu</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Programme, en anglais</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Un programme Fortran s'ouvre par `program nom` et se ferme par `end program nom`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>FO-03</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Terminer le programme jeu</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>end program jeu</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>end program</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>stop jeu</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>end jeu</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>end program, et le nom</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Depuis Fortran 90, `end program jeu` ; dans les vieux programmes, un simple `end`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FO-04</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Interdire les déclarations implicites de variables</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>implicit none</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>implicit off</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>explicit all</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Implicite : aucun</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Sans cette ligne, les variables qui commencent par I à N sont des entiers, et les autres des réels !</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>FO-05</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Déclarer l'entier n</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>integer :: n</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>integer n</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>int :: n</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>n: integer</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Le type, puis deux fois deux-points</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Le `::` est la syntaxe moderne. Les anciens programmes écrivaient `integer n`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>FO-06</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Déclarer le réel x</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>real :: x</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>real x</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>float :: x</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>double :: x</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Réel, en anglais</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>`real` stocke les nombres à virgule. `double precision` en stocke de plus précis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>FO-07</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Mettre la valeur 5 dans la variable n</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>n = 5</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>n := 5</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>let n = 5</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Un simple signe égal</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>L'affectation s'écrit `n = 5`. La comparaison s'écrit `==`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>FO-08</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Afficher la valeur de la variable n</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>print *, n</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>write(*,*) n</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>print n</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>print *, 'n'</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>print, étoile, virgule, puis le nom</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Sans apostrophes, Fortran affiche la valeur de n.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>FO-09</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Lire une saisie au clavier dans la variable n</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>read *, n</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>read(*,*) n</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>input n</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>scan *, n</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Lire, en anglais, sur le même modèle que print</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>`read *, n` lit au clavier en format libre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>FO-10</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Écrire un commentaire contenant note</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>! note</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>re:^!.*</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t># note</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>// note</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Un point d'exclamation</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>En Fortran moderne, `!` commente la fin de ligne. En Fortran 77, on mettait un C en colonne 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>FO-11</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Calculer 2 puissance 8</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2**8</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2 ** 8</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2^8</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>pow(2, 8)</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Deux étoiles</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Fortran a inventé `**` pour la puissance, repris ensuite par Python.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>FO-12</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Calculer la racine carrée de 16.0</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>sqrt(16.0)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>sqrt(16.)</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>sqr(16.0)</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>root(16.0)</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Square root</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>`sqrt` attend un réel : `sqrt(16)` avec un entier provoque une erreur de compilation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>FO-13</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Calculer la valeur absolue de -7</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>abs(-7)</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>absolute(-7)</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>fabs(-7)</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Trois lettres</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>`abs` fonctionne avec les entiers comme avec les réels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>FO-14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Écrire la valeur logique vrai</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>.true.</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Entourée de points</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Les valeurs logiques s'écrivent `.true.` et `.false.`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>FO-15</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Quel opérateur moderne signifie « différent de » ?</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>/=</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>.ne.</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>!=</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>&lt;&gt;</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Une barre oblique et un égal</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>`/=` rappelle le signe ≠. L'ancienne forme est `.ne.` (not equal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>FO-16</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Écrire l'opérateur logique ET</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>.and.</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>&amp;&amp;</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Le mot anglais, entouré de points</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Les opérateurs logiques s'écrivent `.and.`, `.or.` et `.not.`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>FO-17</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Tester si a est égal à b</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>a == b</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>a .eq. b</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>a = b</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>a === b</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Deux signes égal</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>`==` compare. L'ancienne forme est `.eq.` (equal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>FO-18</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Déclarer nom, une chaîne de 10 caractères</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>character(len=10) :: nom</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>character(10) :: nom</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>character*10 nom</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>character*10 :: nom</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>string(10) :: nom</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>char(10) :: nom</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>character, et la longueur</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>La longueur est fixe : le texte est complété par des espaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FO-19</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Arrêter le programme immédiatement</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>halt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Le mot anglais</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>`stop` arrête tout. `exit` ne sort que d'une boucle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FO-20</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Concaténer les chaînes 'ab' et 'cd'</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>'ab' // 'cd'</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>'ab' + 'cd'</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>'ab' &amp; 'cd'</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Deux barres obliques</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>`//` colle deux chaînes. En Fortran, `+` ne marche que sur les nombres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>FO-21</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Écrire le début d'une boucle i de 1 à 10</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>do i = 1, 10</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>for i = 1 to 10</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>do i = 1 to 10</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>do, la variable, début, virgule, fin</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>La boucle `do` est la plus ancienne du langage : elle existe depuis 1957.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>FO-22</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Fermer une boucle do</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>end do</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>enddo</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>next i</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>loop</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>end, puis do</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>`end do` (ou `enddo`) ferme la boucle. En Fortran 77, on utilisait une étiquette numérotée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>FO-23</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Écrire le début d'un test : si x est plus grand que 10</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>if (x &gt; 10) then</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>if (x .gt. 10) then</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>if x &gt; 10 then</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>if (x &gt; 10) {</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Les parenthèses sont obligatoires</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>`if (condition) then` puis le bloc, fermé par `end if`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>FO-24</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Fermer un bloc if</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>end if</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>endif</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>fi</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>end, puis if</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>`end if` et `endif` sont équivalents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>FO-25</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Déclarer t, un tableau de 10 réels</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>real :: t(10)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>real t(10)</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>real, dimension(10) :: t</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>real :: t[10]</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>array t(10)</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Des parenthèses, pas des crochets</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Fortran utilise les parenthèses pour les tableaux comme pour les fonctions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>FO-26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Obtenir le premier élément du tableau t</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>t(1)</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>t(0)</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>t[1]</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Les indices commencent à…</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>En Fortran, les tableaux commencent à 1 par défaut, comme en mathématiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>FO-27</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Écrire le début d'une boucle i de 1 à 10, de 2 en 2</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>do i = 1, 10, 2</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>do i = 1, 10 step 2</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>do i = 1, 2, 10</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Un troisième nombre après une virgule</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Le pas vient en dernier : début, fin, pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>FO-28</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Déclarer la constante réelle pi qui vaut 3.14159</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>real, parameter :: pi = 3.14159</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>real :: pi = 3.14159</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>const real :: pi = 3.14159</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Un attribut qui veut dire paramètre</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>`parameter` rend la valeur non modifiable. Sans lui, pi serait une simple variable initialisée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>FO-29</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Calculer le reste de la division de 7 par 2</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>mod(7, 2)</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>7 % 2</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>7 mod 2</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Une fonction de trois lettres</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>`mod(7, 2)` donne 1. Fortran n'a pas d'opérateur de modulo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>FO-30</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Sortir immédiatement d'une boucle do</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>break</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Sortie, en anglais</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>`exit` quitte la boucle. `stop` arrêterait tout le programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>FO-31</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>3</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Écrire le début d'une boucle qui tourne tant que x est positif</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>do while (x &gt; 0)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>do while (x .gt. 0)</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>while (x &gt; 0) do</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>do until (x &gt; 0)</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>do while, et des parenthèses</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>La boucle se ferme aussi par `end do`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>FO-32</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>3</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Passer directement au tour suivant d'une boucle</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>cycle</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Un cycle</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Piège : en Fortran, `continue` ne fait rien du tout. C'est `cycle` qui passe au tour suivant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>FO-33</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>3</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne du sous-programme echange, qui reçoit a et b</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>subroutine echange(a, b)</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>procedure echange(a, b)</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>sub echange(a, b)</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Un sous-programme, en anglais</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Une `subroutine` ne renvoie pas de valeur : elle modifie ses arguments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>FO-34</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>3</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Appeler le sous-programme echange avec x et y</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>call echange(x, y)</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>echange(x, y)</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>gosub echange(x, y)</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Appeler, en anglais</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Une subroutine s'appelle toujours avec `call`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>FO-35</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>3</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne de la fonction carre, qui reçoit x</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>function carre(x)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>real function carre(x)</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>def carre(x)</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>func carre(x)</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Le mot anglais en entier</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Une `function` renvoie une valeur, rangée dans une variable qui porte son nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FO-36</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Déclarer l'argument entier n en lecture seule</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>integer, intent(in) :: n</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>integer, input :: n</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>integer, intent(read) :: n</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Une intention : entrée</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>`intent(in)` interdit de modifier n. Il existe aussi `out` et `inout`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FO-37</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>3</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Déclarer t, un tableau de réels dont la taille sera fixée plus tard</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>real, allocatable :: t(:)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>real, allocatable, dimension(:) :: t</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>real, dynamic :: t(:)</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>real :: t(*)</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Allouable, en anglais</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>`allocatable` crée un tableau dynamique. Le `:` laisse la taille ouverte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>FO-38</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>3</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Réserver la place de 100 éléments dans le tableau t</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>allocate(t(100))</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>t = new real(100)</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>malloc(t, 100)</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Allouer, en anglais</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>`allocate` réserve la mémoire, `deallocate(t)` la libère.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>FO-39</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>3</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Afficher le réel x sur 6 caractères avec 2 décimales</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>print '(f6.2)', x</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>print "(f6.2)", x</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>write(*, '(f6.2)') x</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>print '(6.2f)', x</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>printf('%6.2f', x)</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Un format entre parenthèses : f, largeur, point, décimales</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>`f6.2` réserve 6 caractères dont 2 décimales. `i5` affiche un entier sur 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>FO-40</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>fortran</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>3</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Utiliser le module maths</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>use maths</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>import maths</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>require maths</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Utiliser, en anglais</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>`use` se place juste après la ligne program ou subroutine, avant implicit none.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/NoobToRoot.xlsx
+++ b/NoobToRoot.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N181"/>
+  <dimension ref="A1:N241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col width="5.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9518,6 +9518,2871 @@
       <c r="N181" t="inlineStr">
         <is>
           <t>`&amp;lt;` affiche &lt; sans ouvrir de balise. De même `&amp;gt;` pour &gt; et `&amp;amp;` pour &amp;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PR-01</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Créer une fenêtre de 400 × 400 pixels</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>size(400, 400);</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>window(400, 400);</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>createCanvas(400, 400);</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Taille, en anglais</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>`size(largeur, hauteur)` crée la fenêtre. En p5.js, on écrit `createCanvas(400, 400)`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PR-02</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Peindre le fond en noir</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>background(0);</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>background(0, 0, 0);</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>fill(0);</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>bg(0);</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>L'arrière-plan, en anglais</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Une seule valeur donne un gris : 0 pour le noir, 255 pour le blanc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PR-03</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Remplir les formes suivantes en rouge</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>fill(255, 0, 0);</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>stroke(255, 0, 0);</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>color(255, 0, 0);</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Remplir, en anglais, puis rouge, vert, bleu</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>`fill(r, g, b)` colore l'intérieur des formes dessinées ensuite. Chaque canal va de 0 à 255.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PR-04</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Donner un contour bleu aux formes suivantes</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>stroke(0, 0, 255);</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>fill(0, 0, 255);</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>border(0, 0, 255);</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Le trait, en anglais</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>`stroke` colore le contour, `fill` l'intérieur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>PR-05</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Dessiner un cercle de 50 pixels de diamètre au point (200, 200)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>ellipse(200, 200, 50, 50);</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>circle(200, 200, 50);</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>circle(200, 200, 25);</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>ellipse(200, 200, 50);</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Une ellipse aussi large que haute</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>`ellipse(x, y, largeur, hauteur)`. `circle(x, y, diamètre)` existe depuis Processing 3.5 : c'est bien le diamètre, pas le rayon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PR-06</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Dessiner un rectangle de 100 × 50 dont le coin supérieur gauche est en (10, 20)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>rect(10, 20, 100, 50);</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>rect(10, 20, 50, 100);</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>rectangle(10, 20, 100, 50);</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Abréviation de rectangle</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>`rect(x, y, largeur, hauteur)` : la largeur vient avant la hauteur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PR-07</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Tracer une ligne du point (0, 0) au point (100, 100)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>line(0, 0, 100, 100);</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>line(0, 100, 0, 100);</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>drawLine(0, 0, 100, 100);</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Ligne, en anglais</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>`line(x1, y1, x2, y2)` : le point de départ, puis le point d'arrivée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>PR-08</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Dessiner un point en (50, 50)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>point(50, 50);</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>pixel(50, 50);</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>dot(50, 50);</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Point, en anglais</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>`point(x, y)` dessine un pixel, avec la couleur et l'épaisseur du contour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>PR-09</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Supprimer le contour des formes suivantes</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>noStroke();</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>stroke(0);</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>noBorder();</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>no + le mot du contour</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>`noStroke()` retire le trait. `stroke(0)` le rendrait noir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>PR-10</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Supprimer le remplissage des formes suivantes</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>noFill();</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>fill(0);</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>transparent();</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>no + le mot du remplissage</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Avec `noFill()`, seul le contour est dessiné.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>PR-11</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Régler l'épaisseur du contour à 4 pixels</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>strokeWeight(4);</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>stroke(4);</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>lineWidth(4);</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Le poids du trait</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>`strokeWeight` règle l'épaisseur. `stroke(4)` donnerait un contour presque noir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PR-12</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Dessiner un carré de 80 pixels de côté, coin supérieur gauche en (10, 10)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>square(10, 10, 80);</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>rect(10, 10, 80, 80);</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>square(10, 10, 80, 80);</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>rect(10, 10, 80);</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Carré, en anglais</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>`square(x, y, côté)`, ou un `rect` aussi large que haut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PR-13</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Afficher Bonjour dans la console</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>println("Bonjour");</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>print("Bonjour");</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>console.log("Bonjour");</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>echo("Bonjour");</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Print line</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>`println` affiche puis passe à la ligne. En p5.js, on utilise `print` ou `console.log`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PR-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Écrire Bonjour dans la fenêtre au point (20, 40)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>text("Bonjour", 20, 40);</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>text(20, 40, "Bonjour");</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>write("Bonjour", 20, 40);</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Texte, en anglais : le texte d'abord, la position ensuite</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>`text(chaîne, x, y)` dessine le texte avec la couleur de `fill`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PR-15</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Régler la taille du texte à 32</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>textSize(32);</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>fontSize(32);</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>textFont(32);</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>text + Size</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>`textSize` change la taille. `textFont` sert à choisir une police chargée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PR-16</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Dessiner un triangle de sommets (0, 100), (50, 0) et (100, 100)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>triangle(0, 100, 50, 0, 100, 100);</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>triangle(0, 100, 50, 0);</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>polygon(0, 100, 50, 0, 100, 100);</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Triangle : trois paires de coordonnées</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>`triangle(x1, y1, x2, y2, x3, y3)` attend six nombres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>PR-17</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Déclarer la variable entière x qui vaut 10</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>int x = 10;</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>x = 10;</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>integer x = 10;</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Le type d'abord, en trois lettres</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Processing vient de Java : chaque variable a un type. `int` pour les entiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>PR-18</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Déclarer la variable décimale vitesse qui vaut 2.5</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>float vitesse = 2.5;</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>int vitesse = 2.5;</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>real vitesse = 2.5;</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Un nombre à virgule flottante</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>`float` stocke les décimaux. Un `int` refuserait 2.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>PR-19</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Quelle variable contient la largeur de la fenêtre ?</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>windowWidth</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Largeur, en anglais</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>`width` et `height` donnent les dimensions fixées par `size()`. `windowWidth` existe seulement en p5.js.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PR-20</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Écrire un commentaire contenant note</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>// note</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>re:^//.*</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>re:^/\*.*\*/$</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t># note</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>&lt;!-- note --&gt;</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Deux barres obliques</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>`//` commente la fin de la ligne, `/* … */` plusieurs lignes, comme en Java et en C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PR-21</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne de la fonction setup</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>void setup() {</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>void setup()</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>function setup() {</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>def setup():</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>void, le nom, des parenthèses, une accolade</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>`setup()` s'exécute une seule fois au lancement. En p5.js, on écrit `function setup() {`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PR-22</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne de la fonction draw</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>void draw() {</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>void draw()</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>void loop() {</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>function draw() {</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Dessiner, en anglais</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>`draw()` est rappelée en boucle, environ 60 fois par seconde : c'est elle qui anime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PR-23</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Quelle variable contient la position horizontale de la souris ?</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>mouseX</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>mouse.x</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>cursorX</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>mouse + l'axe horizontal</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>`mouseX` et `mouseY` sont mises à jour à chaque image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>PR-24</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>2</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Dessiner un cercle de 20 pixels de diamètre qui suit la souris</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>ellipse(mouseX, mouseY, 20, 20);</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>circle(mouseX, mouseY, 20);</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>ellipse(mouseY, mouseX, 20, 20);</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>ellipse(mouse, 20, 20);</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Les coordonnées de la souris à la place des nombres</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Placé dans `draw()`, ce cercle suit la souris. Sans `background()` au début de draw, il laisse une traînée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>PR-25</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Régler l'animation à 30 images par seconde</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>frameRate(30);</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>fps(30);</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>frameCount(30);</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>La cadence des images</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>`frameRate(30)` ralentit draw. `frameCount` est une variable, pas une fonction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>PR-26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Quelle variable compte les images affichées depuis le lancement ?</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>frameCount</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>frameRate</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>frames</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Le compte des images</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>`frameCount` augmente de 1 à chaque passage dans draw : pratique pour animer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>PR-27</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Écrire le début d'une boucle i de 0 à 9</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>for (int i = 0; i &lt; 10; i++) {</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>for (int i = 0; i &lt; 10; i++)</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>for (int i = 0; i &lt;= 9; i++) {</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>for (int i = 0; i &lt;= 9; i++)</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>for i in range(10):</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>for (i = 0 to 9) {</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>for, puis départ ; condition ; incrément</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>La boucle Java : `for (initialisation; condition; incrément)`. N'oublie pas le type `int`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>PR-28</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Écrire le début d'un test : si le bouton de la souris est enfoncé</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>if (mousePressed) {</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>if (mousePressed)</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>if (mousePressed == true) {</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>if (mousePressed == true)</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>if (mouseClicked) {</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>if mousePressed {</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Une variable booléenne de la souris</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>`mousePressed` vaut true tant que le bouton est enfoncé. Les parenthèses sont obligatoires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PR-29</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Tirer un nombre décimal au hasard entre 0 et 100</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>random(100);</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>random(0, 100);</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>rand(100);</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>random();</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Hasard, en anglais</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>`random(100)` renvoie un float de 0 à 100. Pour un entier : `int(random(100))`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>PR-30</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne de la fonction appelée à chaque clic de souris</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>void mousePressed() {</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>void mousePressed()</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>void onClick() {</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>void click() {</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Le même nom que la variable, mais en fonction</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Processing appelle automatiquement `mousePressed()` à chaque appui sur le bouton.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>PR-31</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne de la fonction appelée quand on appuie sur une touche</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>void keyPressed() {</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>void keyPressed()</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>void onKey() {</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>void keyDown() {</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>key + Pressed</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Dans `keyPressed()`, la variable `key` contient la touche tapée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PR-32</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Quelle variable contient la dernière touche tapée ?</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>keyCode</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>lastKey</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Touche, en anglais</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>`key` contient le caractère. `keyCode` sert aux touches spéciales comme les flèches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>PR-33</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Remplir en rouge à moitié transparent</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>fill(255, 0, 0, 128);</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>fill(255, 0, 0, 127);</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>fill(255, 0, 0, 0.5);</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>fill(rgba(255, 0, 0, 128));</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Un quatrième nombre, de 0 à 255</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Le 4e paramètre est l'opacité (alpha) : 0 invisible, 255 opaque, donc environ 128 pour la moitié.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PR-34</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>2</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Faire dessiner les ellipses à partir de leur coin supérieur gauche</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>ellipseMode(CORNER);</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>ellipseMode(corner);</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>rectMode(CORNER);</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Le mode des ellipses, en majuscules</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Par défaut, les ellipses sont centrées (CENTER). Les constantes s'écrivent en majuscules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>PR-35</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Faire dessiner les rectangles à partir de leur centre</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>rectMode(CENTER);</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>rectMode(center);</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>rectAlign(CENTER);</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Le mode des rectangles</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Par défaut, les rectangles partent de leur coin (CORNER).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>PR-36</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Arrêter la boucle de draw</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>noLoop();</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>stop();</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>noDraw();</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>no + boucle</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>`noLoop()` fige l'animation, `loop()` la relance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>PR-37</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Ranger la couleur rouge dans la variable c</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>color c = color(255, 0, 0);</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Color c = color(255, 0, 0);</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>color c = (255, 0, 0);</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Le type color, en minuscules</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>`color` est un type propre à Processing. On l'utilise ensuite avec `fill(c)`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>PR-38</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Charger l'image chat.jpg dans la variable img, déjà déclarée</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>img = loadImage("chat.jpg");</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>PImage img = loadImage("chat.jpg");</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>img = image("chat.jpg");</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>img = load("chat.jpg");</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Charger une image, en un seul mot</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>`loadImage` cherche le fichier dans le dossier data du sketch. Le type est `PImage`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>PR-39</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Afficher l'image img au point (0, 0)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>image(img, 0, 0);</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>draw(img, 0, 0);</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>img(0, 0);</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Image, en anglais</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>`image(img, x, y)` ; on peut ajouter largeur et hauteur pour la redimensionner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PR-40</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Calculer la distance entre les points (x1, y1) et (x2, y2)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>dist(x1, y1, x2, y2);</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>distance(x1, y1, x2, y2);</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>dist(x1, x2, y1, y2);</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Abréviation de distance</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>`dist` renvoie la distance en ligne droite. Pratique pour savoir si la souris touche un cercle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>PR-41</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>3</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Déplacer l'origine du repère au centre de la fenêtre</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>translate(width/2, height/2);</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>translate(width*0.5, height*0.5);</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>translate(width, height);</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>origin(width/2, height/2);</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Translater, en anglais, avec width et height</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Après `translate`, le point (0, 0) est au centre : idéal avant une rotation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>PR-42</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>3</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Faire tourner le repère de 45 degrés</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>rotate(radians(45));</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>rotate(PI/4);</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>rotate(QUARTER_PI);</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>rotate(45);</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>rotation(PI/4);</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>rotate attend des radians</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>`rotate(45)` tournerait de 45 radians ! On convertit avec `radians()`, ou on écrit `PI/4`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>PR-43</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>3</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Sauvegarder l'état du repère avant une transformation</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>pushMatrix();</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>push();</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>saveMatrix();</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>pushStyle();</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>Pousser la matrice sur la pile</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>`pushMatrix()` mémorise le repère, `popMatrix()` le restaure. En p5.js : `push()` et `pop()`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>PR-44</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>3</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Restaurer l'état du repère sauvegardé</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>popMatrix();</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>pop();</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>restoreMatrix();</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>popStyle();</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>Le contraire de push</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Chaque `pushMatrix()` doit avoir son `popMatrix()`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>PR-45</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>3</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Convertir mouseX, qui va de 0 à width, en une valeur de 0 à 255</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>map(mouseX, 0, width, 0, 255);</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>map(0, 255, mouseX, 0, width);</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>scale(mouseX, 0, width, 0, 255);</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>La valeur, l'intervalle de départ, l'intervalle d'arrivée</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>`map(valeur, début1, fin1, début2, fin2)` : la règle de trois en une fonction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>PR-46</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>3</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Limiter la variable v entre 0 et 100</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>constrain(v, 0, 100);</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>clamp(v, 0, 100);</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>limit(v, 0, 100);</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>Contraindre, en anglais</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>`constrain` renvoie 0 si v est trop petit, 100 s'il est trop grand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>PR-47</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>3</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Obtenir une valeur de bruit de Perlin pour le temps t</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>noise(t);</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>perlin(t);</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>random(t);</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>Bruit, en anglais</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>`noise` donne des valeurs aléatoires qui varient en douceur : idéal pour des mouvements organiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>PR-48</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>3</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Déclarer tab, un tableau de 10 décimaux</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>float[] tab = new float[10];</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>float tab[] = new float[10];</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>float tab = new float[10];</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>float[10] tab;</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Le type avec des crochets, puis new</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Syntaxe Java : `type[] nom = new type[taille];`. Les indices vont de 0 à 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>PR-49</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>3</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Obtenir la taille du tableau tab</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>tab.length</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>tab.length()</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>len(tab)</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>Une propriété, sans parenthèses</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Pour un tableau, `length` s'écrit sans parenthèses. Pour une String, c'est `length()`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>PR-50</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>3</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Ajouter 5 à la fin de la liste ArrayList nommée liste</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>liste.add(5);</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>liste.push(5);</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>liste.append(5);</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Ajouter, en anglais</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>`add` pour une ArrayList en Java. `push` est la méthode des tableaux JavaScript, donc en p5.js.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>PR-51</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>3</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Écrire la première ligne de la classe Balle</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>class Balle {</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>class Balle</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>function Balle() {</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>struct Balle {</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Classe, en anglais, nom en majuscule</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Une classe regroupe des variables et des fonctions : `x`, `y`, `bouger()`, `afficher()`…</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PR-52</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>3</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Créer un objet Balle dans la variable b</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Balle b = new Balle();</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>b = new Balle();</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Balle b = Balle();</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Balle b = create Balle();</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Le mot-clé new</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>`new` appelle le constructeur de la classe et crée l'objet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PR-53</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>3</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Passer en mode couleur teinte, saturation, luminosité</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>colorMode(HSB);</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>colorMode(HSB, 360, 100, 100);</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>colorMode(HSL);</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>colorMode("HSB");</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>Hue, Saturation, Brightness</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>En HSB, `fill(0, 100, 100)` donne un rouge vif. Pratique pour faire des dégradés de teintes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PR-54</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>3</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Enregistrer l'image affichée dans le fichier dessin.png</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>save("dessin.png");</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>saveFrame("dessin.png");</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>export("dessin.png");</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>screenshot("dessin.png");</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Sauvegarder, en anglais</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>`saveFrame("image-####.png")` numérote automatiquement les images : parfait pour fabriquer une vidéo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PR-55</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>3</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Activer le lissage des contours au niveau 8</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>smooth(8);</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>antialias(8);</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>smooth(true);</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>Lisser, en anglais</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>`smooth(8)` règle l'anticrénelage. Il s'appelle dans `setup()`, juste après `size()`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PR-56</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>3</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>En p5.js : créer une toile de 400 × 400</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>createCanvas(400, 400);</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>size(400, 400);</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>canvas(400, 400);</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>Créer une toile, en anglais</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>p5.js remplace `size()` par `createCanvas()`. Le reste du dessin se ressemble beaucoup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>PR-57</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>3</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>En p5.js : écrire la première ligne de la fonction setup</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>function setup() {</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>function setup()</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>void setup() {</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>def setup():</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Le mot-clé des fonctions JavaScript</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>p5.js est en JavaScript : `function` remplace `void`, et les variables n'ont pas de type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>PR-58</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>3</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>En p5.js : afficher Bonjour dans la console du navigateur</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>console.log("Bonjour");</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>print("Bonjour");</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>println("Bonjour");</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>echo("Bonjour");</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>La console de JavaScript</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>`println` n'existe qu'en Processing. En p5.js, `print` ou `console.log`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>PR-59</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>3</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>En p5.js : déclarer la variable x qui vaut 10</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>let x = 10;</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>var x = 10;</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>int x = 10;</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>x := 10;</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Un mot-clé JavaScript, sans type</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>En JavaScript, `let` déclare une variable sans préciser son type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>PR-60</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>processing</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>3</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>En p5.js : quelle variable contient la largeur de la fenêtre du navigateur ?</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>windowWidth</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>screenWidth</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>window + Width</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>`width` est la largeur de la toile, `windowWidth` celle de la fenêtre du navigateur.</t>
         </is>
       </c>
     </row>
